--- a/LFP-25-26.xlsx
+++ b/LFP-25-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AA-DADES\Arxius-Python\Liga 25-26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D069A6-7F5B-488B-92DC-4EE628714C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_5654C69DB9B164124A52C131FB48D79791E850AB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34620" yWindow="1515" windowWidth="21600" windowHeight="12975" firstSheet="30" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15720" firstSheet="28" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jornada1" sheetId="1" r:id="rId1"/>
@@ -50,13 +50,14 @@
     <sheet name="Jornada35" sheetId="35" r:id="rId35"/>
     <sheet name="Jornada36" sheetId="36" r:id="rId36"/>
     <sheet name="Jornada37" sheetId="37" r:id="rId37"/>
+    <sheet name="Jornada38" sheetId="38" r:id="rId38"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="24">
   <si>
     <t>Local</t>
   </si>
@@ -6312,10 +6313,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
@@ -6496,6 +6493,200 @@
       </c>
       <c r="D11" t="s">
         <v>21</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
       </c>
       <c r="E11">
         <v>1</v>
